--- a/data/dividends_info_20260805.xlsx
+++ b/data/dividends_info_20260805.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.55500030517578</v>
+        <v>46.16500091552734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1933197280851359</v>
+        <v>0.194952882519556</v>
       </c>
       <c r="J2" t="n">
         <v>222</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.19999694824219</v>
+        <v>67</v>
       </c>
       <c r="I3" t="n">
-        <v>1.041666713971942</v>
+        <v>1.044776119402985</v>
       </c>
       <c r="J3" t="n">
         <v>201</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J5" t="n">
         <v>131</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.55500030517578</v>
+        <v>46.16500091552734</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1933197280851359</v>
+        <v>0.194952882519556</v>
       </c>
       <c r="J6" t="n">
         <v>131</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.160000085830688</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.564814673161806</v>
+        <v>3.598130664738818</v>
       </c>
       <c r="J7" t="n">
         <v>110</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.36499977111816</v>
+        <v>23.08499908447266</v>
       </c>
       <c r="I8" t="n">
-        <v>1.155574588679223</v>
+        <v>1.169590689659617</v>
       </c>
       <c r="J8" t="n">
         <v>110</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.019999980926514</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>3.322259146738715</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J9" t="n">
         <v>103</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.849999904632568</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7643312194767268</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J10" t="n">
         <v>75</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J11" t="n">
         <v>75</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.059999942779541</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.76</v>
       </c>
       <c r="J13" t="n">
         <v>54</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.36499977111816</v>
+        <v>23.08499908447266</v>
       </c>
       <c r="I14" t="n">
-        <v>1.155574588679223</v>
+        <v>1.169590689659617</v>
       </c>
       <c r="J14" t="n">
         <v>47</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.005000114440918</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="I15" t="n">
-        <v>2.842892605813846</v>
+        <v>2.878787851056303</v>
       </c>
       <c r="J15" t="n">
         <v>47</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>46.55500030517578</v>
+        <v>46.16500091552734</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1933197280851359</v>
+        <v>0.194952882519556</v>
       </c>
       <c r="J16" t="n">
         <v>47</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>99.69999694824219</v>
+        <v>97.25</v>
       </c>
       <c r="I17" t="n">
-        <v>1.334002046851065</v>
+        <v>1.367609254498715</v>
       </c>
       <c r="J17" t="n">
         <v>47</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.78000020980835</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="I18" t="n">
-        <v>5.190311230281897</v>
+        <v>5.208333126372769</v>
       </c>
       <c r="J18" t="n">
         <v>40</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.019999980926514</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>7.284768257929115</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.059999942779541</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7509881507849578</v>
+        <v>0.76</v>
       </c>
       <c r="J21" t="n">
         <v>-2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.839999914169312</v>
+        <v>2.730000019073486</v>
       </c>
       <c r="I23" t="n">
-        <v>5.210176213800356</v>
+        <v>5.420109852241615</v>
       </c>
       <c r="J23" t="n">
         <v>-2</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.730000019073486</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I24" t="n">
-        <v>4.363001730677547</v>
+        <v>4.385965059044991</v>
       </c>
       <c r="J24" t="n">
         <v>-9</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.119999885559082</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>3.398058346814786</v>
+        <v>3.373493898380374</v>
       </c>
       <c r="J25" t="n">
         <v>-16</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10.05599975585938</v>
+        <v>9.949999809265137</v>
       </c>
       <c r="I26" t="n">
-        <v>2.585521144712684</v>
+        <v>2.613065376723887</v>
       </c>
       <c r="J26" t="n">
         <v>-16</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.68000030517578</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="I27" t="n">
-        <v>4.385964814437847</v>
+        <v>4.379562104768991</v>
       </c>
       <c r="J27" t="n">
         <v>-16</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.674000024795532</v>
+        <v>2.645999908447266</v>
       </c>
       <c r="I28" t="n">
-        <v>8.227374643230318</v>
+        <v>8.314437173548548</v>
       </c>
       <c r="J28" t="n">
         <v>-16</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J29" t="n">
         <v>-16</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.65500020980835</v>
+        <v>6.534999847412109</v>
       </c>
       <c r="I30" t="n">
-        <v>1.50262955443062</v>
+        <v>1.530221917902576</v>
       </c>
       <c r="J30" t="n">
         <v>-16</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.670000076293945</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I33" t="n">
-        <v>2.116402087924397</v>
+        <v>2.120141399913057</v>
       </c>
       <c r="J33" t="n">
         <v>-23</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.019999980926514</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>4.966887448588033</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J35" t="n">
         <v>-23</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.140000104904175</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I36" t="n">
-        <v>3.971962422114281</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J36" t="n">
         <v>-30</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>38.54999923706055</v>
+        <v>39.20000076293945</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3891050660665008</v>
+        <v>0.3826530537770124</v>
       </c>
       <c r="J38" t="n">
         <v>-30</v>
@@ -3383,78 +3383,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>